--- a/Impfquoten/Impfquoten-11.04.2021.xlsx
+++ b/Impfquoten/Impfquoten-11.04.2021.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23901"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20371"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projekte\Pandemie\Impfquoten\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\Projekte\Abt3_IQM-COVID19\Fachlich\Auswertungen\2021-04-12\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1BCE07EF-4EE6-42E8-BE13-2F8465AB899A}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE9BA704-1F03-43D0-986D-EB9338864707}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="833" yWindow="-98" windowWidth="18465" windowHeight="10996" tabRatio="825" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="120" yWindow="105" windowWidth="28515" windowHeight="12600" tabRatio="825" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Erläuterung" sheetId="9" r:id="rId1"/>
@@ -273,9 +273,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
   </numFmts>
   <fonts count="13" x14ac:knownFonts="1">
     <font>
@@ -538,7 +538,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -618,7 +618,7 @@
     <xf numFmtId="3" fontId="3" fillId="8" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="8" borderId="2" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="8" borderId="2" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="10" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -627,7 +627,7 @@
     <xf numFmtId="3" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="10" fillId="0" borderId="5" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="5" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="5" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="5" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="10" fillId="0" borderId="5" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -677,6 +677,15 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -694,15 +703,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1074,115 +1074,115 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5241AA5B-8CBB-47B1-9317-352256D0A517}">
   <dimension ref="A1:C27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="214.59765625" style="3" customWidth="1"/>
-    <col min="2" max="16384" width="11.3984375" style="3"/>
+    <col min="1" max="1" width="214.5703125" style="3" customWidth="1"/>
+    <col min="2" max="16384" width="11.42578125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>71</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="2"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
       <c r="B4" s="1"/>
       <c r="C4" s="2"/>
     </row>
-    <row r="5" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="11"/>
     </row>
-    <row r="12" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="56" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="20" spans="1:1" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:1" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="57" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="58" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>41</v>
       </c>
@@ -1196,122 +1196,122 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47A1EB7E-F725-49E9-9B87-E64B6D1D2BBC}">
   <dimension ref="A1:T30"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.73046875" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.1328125" customWidth="1"/>
-    <col min="4" max="4" width="13.3984375" style="7" customWidth="1"/>
-    <col min="5" max="5" width="13.59765625" style="7" customWidth="1"/>
-    <col min="6" max="7" width="11.3984375" style="3"/>
+    <col min="3" max="3" width="18.140625" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" style="7" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" style="7" customWidth="1"/>
+    <col min="6" max="7" width="11.42578125" style="3"/>
     <col min="9" max="9" width="13" style="7" customWidth="1"/>
-    <col min="10" max="10" width="12.265625" style="3" customWidth="1"/>
+    <col min="10" max="10" width="12.28515625" style="3" customWidth="1"/>
     <col min="11" max="11" width="10" customWidth="1"/>
-    <col min="13" max="14" width="11.3984375" style="7"/>
-    <col min="15" max="15" width="12.73046875" style="7" customWidth="1"/>
-    <col min="16" max="16" width="12.59765625" customWidth="1"/>
-    <col min="17" max="17" width="9.59765625" customWidth="1"/>
-    <col min="18" max="18" width="12.86328125" customWidth="1"/>
-    <col min="20" max="20" width="18.3984375" customWidth="1"/>
+    <col min="13" max="14" width="11.42578125" style="7"/>
+    <col min="15" max="15" width="12.7109375" style="7" customWidth="1"/>
+    <col min="16" max="16" width="12.5703125" customWidth="1"/>
+    <col min="17" max="17" width="9.5703125" customWidth="1"/>
+    <col min="18" max="18" width="12.85546875" customWidth="1"/>
+    <col min="20" max="20" width="18.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="66" t="s">
+    <row r="1" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="69" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="66" t="s">
+      <c r="B1" s="69" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="69" t="s">
+      <c r="C1" s="72" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="69"/>
-      <c r="G1" s="69"/>
-      <c r="H1" s="69"/>
-      <c r="I1" s="69"/>
-      <c r="J1" s="69"/>
-      <c r="K1" s="69"/>
-      <c r="L1" s="69" t="s">
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
+      <c r="J1" s="72"/>
+      <c r="K1" s="72"/>
+      <c r="L1" s="72" t="s">
         <v>44</v>
       </c>
-      <c r="M1" s="69"/>
-      <c r="N1" s="69"/>
-      <c r="O1" s="69"/>
-      <c r="P1" s="69" t="s">
+      <c r="M1" s="72"/>
+      <c r="N1" s="72"/>
+      <c r="O1" s="72"/>
+      <c r="P1" s="72" t="s">
         <v>63</v>
       </c>
-      <c r="Q1" s="69"/>
-      <c r="R1" s="69"/>
-      <c r="S1" s="69"/>
-    </row>
-    <row r="2" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="67"/>
-      <c r="B2" s="67"/>
-      <c r="C2" s="70" t="s">
+      <c r="Q1" s="72"/>
+      <c r="R1" s="72"/>
+      <c r="S1" s="72"/>
+    </row>
+    <row r="2" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="70"/>
+      <c r="B2" s="70"/>
+      <c r="C2" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="66" t="s">
+      <c r="D2" s="69" t="s">
         <v>57</v>
       </c>
-      <c r="E2" s="66" t="s">
+      <c r="E2" s="69" t="s">
         <v>58</v>
       </c>
-      <c r="F2" s="70" t="s">
+      <c r="F2" s="73" t="s">
         <v>53</v>
       </c>
-      <c r="G2" s="70"/>
-      <c r="H2" s="70"/>
-      <c r="I2" s="70" t="s">
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73" t="s">
         <v>54</v>
       </c>
-      <c r="J2" s="70"/>
-      <c r="K2" s="70"/>
-      <c r="L2" s="71" t="s">
+      <c r="J2" s="73"/>
+      <c r="K2" s="73"/>
+      <c r="L2" s="74" t="s">
         <v>51</v>
       </c>
-      <c r="M2" s="71"/>
-      <c r="N2" s="71" t="s">
+      <c r="M2" s="74"/>
+      <c r="N2" s="74" t="s">
         <v>52</v>
       </c>
-      <c r="O2" s="71"/>
-      <c r="P2" s="71" t="s">
+      <c r="O2" s="74"/>
+      <c r="P2" s="74" t="s">
         <v>51</v>
       </c>
-      <c r="Q2" s="71"/>
-      <c r="R2" s="71" t="s">
+      <c r="Q2" s="74"/>
+      <c r="R2" s="74" t="s">
         <v>52</v>
       </c>
-      <c r="S2" s="71"/>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.45">
-      <c r="A3" s="67"/>
-      <c r="B3" s="67"/>
-      <c r="C3" s="70"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="70"/>
-      <c r="H3" s="70"/>
-      <c r="I3" s="70"/>
-      <c r="J3" s="70"/>
-      <c r="K3" s="70"/>
-      <c r="L3" s="71"/>
-      <c r="M3" s="71"/>
-      <c r="N3" s="71"/>
-      <c r="O3" s="71"/>
-      <c r="P3" s="71"/>
-      <c r="Q3" s="71"/>
-      <c r="R3" s="71"/>
-      <c r="S3" s="71"/>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.45">
-      <c r="A4" s="68"/>
-      <c r="B4" s="68"/>
-      <c r="C4" s="70"/>
-      <c r="D4" s="68"/>
-      <c r="E4" s="68"/>
+      <c r="S2" s="74"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" s="70"/>
+      <c r="B3" s="70"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="70"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="73"/>
+      <c r="K3" s="73"/>
+      <c r="L3" s="74"/>
+      <c r="M3" s="74"/>
+      <c r="N3" s="74"/>
+      <c r="O3" s="74"/>
+      <c r="P3" s="74"/>
+      <c r="Q3" s="74"/>
+      <c r="R3" s="74"/>
+      <c r="S3" s="74"/>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" s="71"/>
+      <c r="B4" s="71"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="71"/>
+      <c r="E4" s="71"/>
       <c r="F4" s="14" t="s">
         <v>19</v>
       </c>
@@ -1355,7 +1355,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
         <v>25</v>
       </c>
@@ -1414,7 +1414,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="21" t="s">
         <v>26</v>
       </c>
@@ -1473,7 +1473,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="29">
         <v>11</v>
       </c>
@@ -1532,7 +1532,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="21">
         <v>12</v>
       </c>
@@ -1591,7 +1591,7 @@
         <v>1901</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="29" t="s">
         <v>27</v>
       </c>
@@ -1650,7 +1650,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="21" t="s">
         <v>28</v>
       </c>
@@ -1709,7 +1709,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="29" t="s">
         <v>29</v>
       </c>
@@ -1768,7 +1768,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="21">
         <v>13</v>
       </c>
@@ -1827,7 +1827,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="29" t="s">
         <v>30</v>
       </c>
@@ -1886,7 +1886,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="21" t="s">
         <v>31</v>
       </c>
@@ -1945,7 +1945,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="29" t="s">
         <v>32</v>
       </c>
@@ -2004,7 +2004,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="21">
         <v>10</v>
       </c>
@@ -2063,7 +2063,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" s="29">
         <v>14</v>
       </c>
@@ -2122,7 +2122,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" s="21">
         <v>15</v>
       </c>
@@ -2181,7 +2181,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" s="29" t="s">
         <v>33</v>
       </c>
@@ -2240,7 +2240,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" s="21">
         <v>16</v>
       </c>
@@ -2299,7 +2299,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" s="29"/>
       <c r="B21" s="30" t="s">
         <v>50</v>
@@ -2356,7 +2356,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="22" spans="1:20" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="38"/>
       <c r="B22" s="39" t="s">
         <v>19</v>
@@ -2413,137 +2413,132 @@
         <v>5688</v>
       </c>
     </row>
-    <row r="23" spans="1:20" ht="14.65" thickTop="1" x14ac:dyDescent="0.45"/>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A25" s="72" t="s">
+    <row r="23" spans="1:20" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A25" s="66" t="s">
         <v>35</v>
       </c>
-      <c r="B25" s="72"/>
-      <c r="C25" s="72"/>
-      <c r="D25" s="72"/>
-      <c r="E25" s="72"/>
-      <c r="F25" s="72"/>
-      <c r="G25" s="72"/>
-      <c r="H25" s="72"/>
-      <c r="I25" s="72"/>
-      <c r="J25" s="72"/>
-      <c r="K25" s="72"/>
-      <c r="L25" s="72"/>
-      <c r="M25" s="72"/>
-      <c r="N25" s="72"/>
-      <c r="O25" s="72"/>
-      <c r="P25" s="72"/>
-      <c r="Q25" s="72"/>
-      <c r="R25" s="72"/>
-      <c r="S25" s="72"/>
+      <c r="B25" s="66"/>
+      <c r="C25" s="66"/>
+      <c r="D25" s="66"/>
+      <c r="E25" s="66"/>
+      <c r="F25" s="66"/>
+      <c r="G25" s="66"/>
+      <c r="H25" s="66"/>
+      <c r="I25" s="66"/>
+      <c r="J25" s="66"/>
+      <c r="K25" s="66"/>
+      <c r="L25" s="66"/>
+      <c r="M25" s="66"/>
+      <c r="N25" s="66"/>
+      <c r="O25" s="66"/>
+      <c r="P25" s="66"/>
+      <c r="Q25" s="66"/>
+      <c r="R25" s="66"/>
+      <c r="S25" s="66"/>
       <c r="T25" s="54"/>
     </row>
-    <row r="26" spans="1:20" s="7" customFormat="1" ht="45.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="74" t="s">
+    <row r="26" spans="1:20" s="7" customFormat="1" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="68" t="s">
         <v>64</v>
       </c>
-      <c r="B26" s="74"/>
-      <c r="C26" s="74"/>
-      <c r="D26" s="74"/>
-      <c r="E26" s="74"/>
-      <c r="F26" s="74"/>
-      <c r="G26" s="74"/>
-      <c r="H26" s="74"/>
-      <c r="I26" s="74"/>
-      <c r="J26" s="74"/>
-      <c r="K26" s="74"/>
-      <c r="L26" s="74"/>
-      <c r="M26" s="74"/>
-      <c r="N26" s="74"/>
-      <c r="O26" s="74"/>
-      <c r="P26" s="74"/>
-      <c r="Q26" s="74"/>
-      <c r="R26" s="74"/>
-      <c r="S26" s="74"/>
+      <c r="B26" s="68"/>
+      <c r="C26" s="68"/>
+      <c r="D26" s="68"/>
+      <c r="E26" s="68"/>
+      <c r="F26" s="68"/>
+      <c r="G26" s="68"/>
+      <c r="H26" s="68"/>
+      <c r="I26" s="68"/>
+      <c r="J26" s="68"/>
+      <c r="K26" s="68"/>
+      <c r="L26" s="68"/>
+      <c r="M26" s="68"/>
+      <c r="N26" s="68"/>
+      <c r="O26" s="68"/>
+      <c r="P26" s="68"/>
+      <c r="Q26" s="68"/>
+      <c r="R26" s="68"/>
+      <c r="S26" s="68"/>
       <c r="T26" s="55"/>
     </row>
-    <row r="27" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="73" t="s">
+    <row r="27" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="67" t="s">
         <v>65</v>
       </c>
-      <c r="B27" s="73"/>
-      <c r="C27" s="73"/>
-      <c r="D27" s="73"/>
-      <c r="E27" s="73"/>
-      <c r="F27" s="73"/>
-      <c r="G27" s="73"/>
-      <c r="H27" s="73"/>
-      <c r="I27" s="73"/>
-      <c r="J27" s="73"/>
-      <c r="K27" s="73"/>
-      <c r="L27" s="73"/>
-      <c r="M27" s="73"/>
-      <c r="N27" s="73"/>
-      <c r="O27" s="73"/>
-      <c r="P27" s="73"/>
-      <c r="Q27" s="73"/>
-      <c r="R27" s="73"/>
-      <c r="S27" s="73"/>
-      <c r="T27" s="73"/>
-    </row>
-    <row r="28" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="73" t="s">
+      <c r="B27" s="67"/>
+      <c r="C27" s="67"/>
+      <c r="D27" s="67"/>
+      <c r="E27" s="67"/>
+      <c r="F27" s="67"/>
+      <c r="G27" s="67"/>
+      <c r="H27" s="67"/>
+      <c r="I27" s="67"/>
+      <c r="J27" s="67"/>
+      <c r="K27" s="67"/>
+      <c r="L27" s="67"/>
+      <c r="M27" s="67"/>
+      <c r="N27" s="67"/>
+      <c r="O27" s="67"/>
+      <c r="P27" s="67"/>
+      <c r="Q27" s="67"/>
+      <c r="R27" s="67"/>
+      <c r="S27" s="67"/>
+      <c r="T27" s="67"/>
+    </row>
+    <row r="28" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="67" t="s">
         <v>66</v>
       </c>
-      <c r="B28" s="73"/>
-      <c r="C28" s="73"/>
-      <c r="D28" s="73"/>
-      <c r="E28" s="73"/>
-      <c r="F28" s="73"/>
-      <c r="G28" s="73"/>
-      <c r="H28" s="73"/>
-      <c r="I28" s="73"/>
-      <c r="J28" s="73"/>
-      <c r="K28" s="73"/>
-      <c r="L28" s="73"/>
-      <c r="M28" s="73"/>
-      <c r="N28" s="73"/>
-      <c r="O28" s="73"/>
-      <c r="P28" s="73"/>
-      <c r="Q28" s="73"/>
-      <c r="R28" s="73"/>
-      <c r="S28" s="73"/>
-      <c r="T28" s="73"/>
-    </row>
-    <row r="29" spans="1:20" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="74" t="s">
+      <c r="B28" s="67"/>
+      <c r="C28" s="67"/>
+      <c r="D28" s="67"/>
+      <c r="E28" s="67"/>
+      <c r="F28" s="67"/>
+      <c r="G28" s="67"/>
+      <c r="H28" s="67"/>
+      <c r="I28" s="67"/>
+      <c r="J28" s="67"/>
+      <c r="K28" s="67"/>
+      <c r="L28" s="67"/>
+      <c r="M28" s="67"/>
+      <c r="N28" s="67"/>
+      <c r="O28" s="67"/>
+      <c r="P28" s="67"/>
+      <c r="Q28" s="67"/>
+      <c r="R28" s="67"/>
+      <c r="S28" s="67"/>
+      <c r="T28" s="67"/>
+    </row>
+    <row r="29" spans="1:20" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="68" t="s">
         <v>55</v>
       </c>
-      <c r="B29" s="74"/>
-      <c r="C29" s="74"/>
-      <c r="D29" s="74"/>
-      <c r="E29" s="74"/>
-      <c r="F29" s="74"/>
-      <c r="G29" s="74"/>
-      <c r="H29" s="74"/>
-      <c r="I29" s="74"/>
-      <c r="J29" s="74"/>
-      <c r="K29" s="74"/>
-      <c r="L29" s="74"/>
-      <c r="M29" s="74"/>
-      <c r="N29" s="74"/>
-      <c r="O29" s="74"/>
-      <c r="P29" s="74"/>
-      <c r="Q29" s="74"/>
-      <c r="R29" s="74"/>
-      <c r="S29" s="74"/>
-      <c r="T29" s="74"/>
-    </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="B29" s="68"/>
+      <c r="C29" s="68"/>
+      <c r="D29" s="68"/>
+      <c r="E29" s="68"/>
+      <c r="F29" s="68"/>
+      <c r="G29" s="68"/>
+      <c r="H29" s="68"/>
+      <c r="I29" s="68"/>
+      <c r="J29" s="68"/>
+      <c r="K29" s="68"/>
+      <c r="L29" s="68"/>
+      <c r="M29" s="68"/>
+      <c r="N29" s="68"/>
+      <c r="O29" s="68"/>
+      <c r="P29" s="68"/>
+      <c r="Q29" s="68"/>
+      <c r="R29" s="68"/>
+      <c r="S29" s="68"/>
+      <c r="T29" s="68"/>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A30" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A25:S25"/>
-    <mergeCell ref="A27:T27"/>
-    <mergeCell ref="A29:T29"/>
-    <mergeCell ref="A28:T28"/>
-    <mergeCell ref="A26:S26"/>
     <mergeCell ref="A1:A4"/>
     <mergeCell ref="B1:B4"/>
     <mergeCell ref="C1:K1"/>
@@ -2558,6 +2553,11 @@
     <mergeCell ref="R2:S3"/>
     <mergeCell ref="D2:D4"/>
     <mergeCell ref="E2:E4"/>
+    <mergeCell ref="A25:S25"/>
+    <mergeCell ref="A27:T27"/>
+    <mergeCell ref="A29:T29"/>
+    <mergeCell ref="A28:T28"/>
+    <mergeCell ref="A26:S26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2567,20 +2567,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87F4549C-7AD6-45E3-9E9E-50890FFA92FE}">
   <dimension ref="A1:V27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.265625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="3.28515625" style="3" customWidth="1"/>
     <col min="2" max="2" width="23" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="11.3984375" style="3"/>
-    <col min="5" max="5" width="12.73046875" style="3" customWidth="1"/>
+    <col min="3" max="4" width="11.42578125" style="3"/>
+    <col min="5" max="5" width="12.7109375" style="3" customWidth="1"/>
     <col min="6" max="6" width="13" style="3" customWidth="1"/>
-    <col min="7" max="8" width="11.3984375" style="3"/>
-    <col min="9" max="9" width="13.265625" style="3" customWidth="1"/>
-    <col min="10" max="11" width="14.265625" style="3" customWidth="1"/>
-    <col min="12" max="16384" width="11.3984375" style="3"/>
+    <col min="7" max="8" width="11.42578125" style="3"/>
+    <col min="9" max="9" width="13.28515625" style="3" customWidth="1"/>
+    <col min="10" max="11" width="14.28515625" style="3" customWidth="1"/>
+    <col min="12" max="16384" width="11.42578125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="78" t="s">
         <v>34</v>
       </c>
@@ -2612,16 +2612,16 @@
       <c r="U1" s="76"/>
       <c r="V1" s="77"/>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="79"/>
       <c r="B2" s="82"/>
-      <c r="C2" s="69" t="s">
+      <c r="C2" s="72" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
       <c r="H2" s="75" t="s">
         <v>52</v>
       </c>
@@ -2629,13 +2629,13 @@
       <c r="J2" s="76"/>
       <c r="K2" s="76"/>
       <c r="L2" s="77"/>
-      <c r="M2" s="69" t="s">
+      <c r="M2" s="72" t="s">
         <v>51</v>
       </c>
-      <c r="N2" s="69"/>
-      <c r="O2" s="69"/>
-      <c r="P2" s="69"/>
-      <c r="Q2" s="69"/>
+      <c r="N2" s="72"/>
+      <c r="O2" s="72"/>
+      <c r="P2" s="72"/>
+      <c r="Q2" s="72"/>
       <c r="R2" s="75" t="s">
         <v>52</v>
       </c>
@@ -2644,16 +2644,16 @@
       <c r="U2" s="76"/>
       <c r="V2" s="77"/>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="79"/>
       <c r="B3" s="82"/>
-      <c r="C3" s="69" t="s">
+      <c r="C3" s="72" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="69" t="s">
+      <c r="D3" s="72"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="72" t="s">
         <v>17</v>
       </c>
       <c r="H3" s="75" t="s">
@@ -2662,16 +2662,16 @@
       <c r="I3" s="76"/>
       <c r="J3" s="76"/>
       <c r="K3" s="77"/>
-      <c r="L3" s="69" t="s">
+      <c r="L3" s="72" t="s">
         <v>17</v>
       </c>
-      <c r="M3" s="69" t="s">
+      <c r="M3" s="72" t="s">
         <v>20</v>
       </c>
-      <c r="N3" s="69"/>
-      <c r="O3" s="69"/>
-      <c r="P3" s="69"/>
-      <c r="Q3" s="69" t="s">
+      <c r="N3" s="72"/>
+      <c r="O3" s="72"/>
+      <c r="P3" s="72"/>
+      <c r="Q3" s="72" t="s">
         <v>17</v>
       </c>
       <c r="R3" s="75" t="s">
@@ -2680,11 +2680,11 @@
       <c r="S3" s="76"/>
       <c r="T3" s="76"/>
       <c r="U3" s="77"/>
-      <c r="V3" s="69" t="s">
+      <c r="V3" s="72" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="80"/>
       <c r="B4" s="83"/>
       <c r="C4" s="14" t="s">
@@ -2699,7 +2699,7 @@
       <c r="F4" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="G4" s="69"/>
+      <c r="G4" s="72"/>
       <c r="H4" s="14" t="s">
         <v>19</v>
       </c>
@@ -2712,7 +2712,7 @@
       <c r="K4" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="L4" s="69"/>
+      <c r="L4" s="72"/>
       <c r="M4" s="14" t="s">
         <v>19</v>
       </c>
@@ -2725,7 +2725,7 @@
       <c r="P4" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="Q4" s="69"/>
+      <c r="Q4" s="72"/>
       <c r="R4" s="14" t="s">
         <v>19</v>
       </c>
@@ -2738,9 +2738,9 @@
       <c r="U4" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="V4" s="69"/>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="V4" s="72"/>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" s="29" t="s">
         <v>25</v>
       </c>
@@ -2808,7 +2808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" s="21" t="s">
         <v>26</v>
       </c>
@@ -2876,7 +2876,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" s="29">
         <v>11</v>
       </c>
@@ -2944,7 +2944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" s="21">
         <v>12</v>
       </c>
@@ -3012,7 +3012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" s="29" t="s">
         <v>27</v>
       </c>
@@ -3080,7 +3080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" s="21" t="s">
         <v>28</v>
       </c>
@@ -3148,7 +3148,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" s="29" t="s">
         <v>29</v>
       </c>
@@ -3216,7 +3216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" s="21">
         <v>13</v>
       </c>
@@ -3284,7 +3284,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" s="29" t="s">
         <v>30</v>
       </c>
@@ -3352,7 +3352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" s="21" t="s">
         <v>31</v>
       </c>
@@ -3420,7 +3420,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" s="29" t="s">
         <v>32</v>
       </c>
@@ -3488,7 +3488,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" s="21">
         <v>10</v>
       </c>
@@ -3556,7 +3556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17" s="29">
         <v>14</v>
       </c>
@@ -3624,7 +3624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18" s="21">
         <v>15</v>
       </c>
@@ -3692,7 +3692,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19" s="29" t="s">
         <v>33</v>
       </c>
@@ -3760,7 +3760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20" s="21">
         <v>16</v>
       </c>
@@ -3828,7 +3828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A21" s="29"/>
       <c r="B21" s="44" t="s">
         <v>50</v>
@@ -3894,7 +3894,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="22" spans="1:22" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="38"/>
       <c r="B22" s="51" t="s">
         <v>19</v>
@@ -3960,44 +3960,52 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:22" ht="14.65" thickTop="1" x14ac:dyDescent="0.45"/>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:22" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B25" s="7" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B26" s="7" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="27" spans="1:22" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B27" s="74" t="s">
+    <row r="27" spans="1:22" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="68" t="s">
         <v>56</v>
       </c>
-      <c r="C27" s="74"/>
-      <c r="D27" s="74"/>
-      <c r="E27" s="74"/>
-      <c r="F27" s="74"/>
-      <c r="G27" s="74"/>
-      <c r="H27" s="74"/>
-      <c r="I27" s="74"/>
-      <c r="J27" s="74"/>
-      <c r="K27" s="74"/>
-      <c r="L27" s="74"/>
-      <c r="M27" s="74"/>
-      <c r="N27" s="74"/>
-      <c r="O27" s="74"/>
-      <c r="P27" s="74"/>
-      <c r="Q27" s="74"/>
-      <c r="R27" s="74"/>
-      <c r="S27" s="74"/>
-      <c r="T27" s="74"/>
-      <c r="U27" s="74"/>
-      <c r="V27" s="74"/>
+      <c r="C27" s="68"/>
+      <c r="D27" s="68"/>
+      <c r="E27" s="68"/>
+      <c r="F27" s="68"/>
+      <c r="G27" s="68"/>
+      <c r="H27" s="68"/>
+      <c r="I27" s="68"/>
+      <c r="J27" s="68"/>
+      <c r="K27" s="68"/>
+      <c r="L27" s="68"/>
+      <c r="M27" s="68"/>
+      <c r="N27" s="68"/>
+      <c r="O27" s="68"/>
+      <c r="P27" s="68"/>
+      <c r="Q27" s="68"/>
+      <c r="R27" s="68"/>
+      <c r="S27" s="68"/>
+      <c r="T27" s="68"/>
+      <c r="U27" s="68"/>
+      <c r="V27" s="68"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="M1:V1"/>
+    <mergeCell ref="A1:A4"/>
+    <mergeCell ref="B1:B4"/>
+    <mergeCell ref="C1:L1"/>
+    <mergeCell ref="C3:F3"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="H3:K3"/>
+    <mergeCell ref="L3:L4"/>
     <mergeCell ref="B27:V27"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
@@ -4007,14 +4015,6 @@
     <mergeCell ref="Q3:Q4"/>
     <mergeCell ref="R3:U3"/>
     <mergeCell ref="V3:V4"/>
-    <mergeCell ref="M1:V1"/>
-    <mergeCell ref="A1:A4"/>
-    <mergeCell ref="B1:B4"/>
-    <mergeCell ref="C1:L1"/>
-    <mergeCell ref="C3:F3"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="H3:K3"/>
-    <mergeCell ref="L3:L4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="90" verticalDpi="90" r:id="rId1"/>
@@ -4024,16 +4024,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{926B42D2-7956-44E7-BD5B-5AF896796AC0}">
   <dimension ref="A1:D112"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.3984375" style="62"/>
-    <col min="2" max="2" width="11.3984375" style="13"/>
-    <col min="3" max="3" width="13.265625" style="13" customWidth="1"/>
-    <col min="4" max="4" width="16.73046875" style="13" customWidth="1"/>
-    <col min="5" max="16384" width="11.3984375" style="13"/>
+    <col min="1" max="1" width="11.42578125" style="62"/>
+    <col min="2" max="2" width="11.42578125" style="13"/>
+    <col min="3" max="3" width="13.28515625" style="13" customWidth="1"/>
+    <col min="4" max="4" width="16.7109375" style="13" customWidth="1"/>
+    <col min="5" max="16384" width="11.42578125" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" ht="75" x14ac:dyDescent="0.25">
       <c r="A1" s="61" t="s">
         <v>73</v>
       </c>
@@ -4047,7 +4047,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="61">
         <v>44192</v>
       </c>
@@ -4059,7 +4059,7 @@
         <v>24159</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="61">
         <v>44193</v>
       </c>
@@ -4071,7 +4071,7 @@
         <v>18384</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="61">
         <v>44194</v>
       </c>
@@ -4083,7 +4083,7 @@
         <v>48118</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="61">
         <v>44195</v>
       </c>
@@ -4095,7 +4095,7 @@
         <v>61490</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="61">
         <v>44196</v>
       </c>
@@ -4107,7 +4107,7 @@
         <v>49241</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="61">
         <v>44197</v>
       </c>
@@ -4119,7 +4119,7 @@
         <v>19273</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="61">
         <v>44198</v>
       </c>
@@ -4131,7 +4131,7 @@
         <v>52425</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="61">
         <v>44199</v>
       </c>
@@ -4143,7 +4143,7 @@
         <v>24308</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="61">
         <v>44200</v>
       </c>
@@ -4155,7 +4155,7 @@
         <v>48350</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="61">
         <v>44201</v>
       </c>
@@ -4167,7 +4167,7 @@
         <v>53336</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="61">
         <v>44202</v>
       </c>
@@ -4179,7 +4179,7 @@
         <v>62993</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="61">
         <v>44203</v>
       </c>
@@ -4191,7 +4191,7 @@
         <v>56197</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="61">
         <v>44204</v>
       </c>
@@ -4203,7 +4203,7 @@
         <v>63105</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="61">
         <v>44205</v>
       </c>
@@ -4215,7 +4215,7 @@
         <v>61181</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="61">
         <v>44206</v>
       </c>
@@ -4227,7 +4227,7 @@
         <v>35132</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="61">
         <v>44207</v>
       </c>
@@ -4239,7 +4239,7 @@
         <v>66396</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="61">
         <v>44208</v>
       </c>
@@ -4251,7 +4251,7 @@
         <v>82876</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="61">
         <v>44209</v>
       </c>
@@ -4263,7 +4263,7 @@
         <v>111080</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="61">
         <v>44210</v>
       </c>
@@ -4275,7 +4275,7 @@
         <v>82756</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="61">
         <v>44211</v>
       </c>
@@ -4289,7 +4289,7 @@
         <v>90119</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="61">
         <v>44212</v>
       </c>
@@ -4303,7 +4303,7 @@
         <v>57344</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="61">
         <v>44213</v>
       </c>
@@ -4317,7 +4317,7 @@
         <v>47509</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="61">
         <v>44214</v>
       </c>
@@ -4331,7 +4331,7 @@
         <v>81788</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="61">
         <v>44215</v>
       </c>
@@ -4345,7 +4345,7 @@
         <v>113233</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="61">
         <v>44216</v>
       </c>
@@ -4359,7 +4359,7 @@
         <v>131203</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="61">
         <v>44217</v>
       </c>
@@ -4373,7 +4373,7 @@
         <v>103939</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="61">
         <v>44218</v>
       </c>
@@ -4387,7 +4387,7 @@
         <v>101781</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="61">
         <v>44219</v>
       </c>
@@ -4401,7 +4401,7 @@
         <v>85365</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="61">
         <v>44220</v>
       </c>
@@ -4415,7 +4415,7 @@
         <v>49153</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="61">
         <v>44221</v>
       </c>
@@ -4429,7 +4429,7 @@
         <v>95873</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="61">
         <v>44222</v>
       </c>
@@ -4443,7 +4443,7 @@
         <v>99027</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="61">
         <v>44223</v>
       </c>
@@ -4457,7 +4457,7 @@
         <v>110908</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="61">
         <v>44224</v>
       </c>
@@ -4471,7 +4471,7 @@
         <v>91252</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="61">
         <v>44225</v>
       </c>
@@ -4485,7 +4485,7 @@
         <v>108457</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="61">
         <v>44226</v>
       </c>
@@ -4499,7 +4499,7 @@
         <v>86340</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="61">
         <v>44227</v>
       </c>
@@ -4513,7 +4513,7 @@
         <v>57423</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="61">
         <v>44228</v>
       </c>
@@ -4527,7 +4527,7 @@
         <v>121109</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="61">
         <v>44229</v>
       </c>
@@ -4541,7 +4541,7 @@
         <v>130296</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="61">
         <v>44230</v>
       </c>
@@ -4555,7 +4555,7 @@
         <v>157629</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="61">
         <v>44231</v>
       </c>
@@ -4569,7 +4569,7 @@
         <v>130904</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="61">
         <v>44232</v>
       </c>
@@ -4583,7 +4583,7 @@
         <v>142667</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="61">
         <v>44233</v>
       </c>
@@ -4597,7 +4597,7 @@
         <v>99071</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="61">
         <v>44234</v>
       </c>
@@ -4611,7 +4611,7 @@
         <v>53537</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="61">
         <v>44235</v>
       </c>
@@ -4625,7 +4625,7 @@
         <v>109852</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="61">
         <v>44236</v>
       </c>
@@ -4639,7 +4639,7 @@
         <v>132393</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="61">
         <v>44237</v>
       </c>
@@ -4653,7 +4653,7 @@
         <v>148704</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="61">
         <v>44238</v>
       </c>
@@ -4667,7 +4667,7 @@
         <v>141785</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="61">
         <v>44239</v>
       </c>
@@ -4681,7 +4681,7 @@
         <v>155904</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="61">
         <v>44240</v>
       </c>
@@ -4695,7 +4695,7 @@
         <v>107660</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="61">
         <v>44241</v>
       </c>
@@ -4709,7 +4709,7 @@
         <v>64795</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="61">
         <v>44242</v>
       </c>
@@ -4723,7 +4723,7 @@
         <v>126328</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="61">
         <v>44243</v>
       </c>
@@ -4737,7 +4737,7 @@
         <v>134326</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="61">
         <v>44244</v>
       </c>
@@ -4751,7 +4751,7 @@
         <v>149725</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="61">
         <v>44245</v>
       </c>
@@ -4765,7 +4765,7 @@
         <v>143464</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="61">
         <v>44246</v>
       </c>
@@ -4779,7 +4779,7 @@
         <v>152306</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="61">
         <v>44247</v>
       </c>
@@ -4793,7 +4793,7 @@
         <v>114040</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="61">
         <v>44248</v>
       </c>
@@ -4807,7 +4807,7 @@
         <v>85768</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="61">
         <v>44249</v>
       </c>
@@ -4821,7 +4821,7 @@
         <v>160466</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="61">
         <v>44250</v>
       </c>
@@ -4835,7 +4835,7 @@
         <v>166330</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="61">
         <v>44251</v>
       </c>
@@ -4849,7 +4849,7 @@
         <v>173964</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="61">
         <v>44252</v>
       </c>
@@ -4863,7 +4863,7 @@
         <v>188039</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="61">
         <v>44253</v>
       </c>
@@ -4877,7 +4877,7 @@
         <v>207471</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="61">
         <v>44254</v>
       </c>
@@ -4891,7 +4891,7 @@
         <v>148185</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="61">
         <v>44255</v>
       </c>
@@ -4905,7 +4905,7 @@
         <v>108089</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="61">
         <v>44256</v>
       </c>
@@ -4919,7 +4919,7 @@
         <v>194230</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="61">
         <v>44257</v>
       </c>
@@ -4933,7 +4933,7 @@
         <v>218238</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="61">
         <v>44258</v>
       </c>
@@ -4947,7 +4947,7 @@
         <v>241461</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="61">
         <v>44259</v>
       </c>
@@ -4961,7 +4961,7 @@
         <v>241235</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="61">
         <v>44260</v>
       </c>
@@ -4975,7 +4975,7 @@
         <v>264466</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="61">
         <v>44261</v>
       </c>
@@ -4989,7 +4989,7 @@
         <v>201964</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="61">
         <v>44262</v>
       </c>
@@ -5003,7 +5003,7 @@
         <v>149211</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="61">
         <v>44263</v>
       </c>
@@ -5017,7 +5017,7 @@
         <v>237744</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="61">
         <v>44264</v>
       </c>
@@ -5031,7 +5031,7 @@
         <v>249860</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="61">
         <v>44265</v>
       </c>
@@ -5045,7 +5045,7 @@
         <v>282212</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="61">
         <v>44266</v>
       </c>
@@ -5059,7 +5059,7 @@
         <v>280130</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="61">
         <v>44267</v>
       </c>
@@ -5073,7 +5073,7 @@
         <v>320435</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="61">
         <v>44268</v>
       </c>
@@ -5087,7 +5087,7 @@
         <v>245669</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="61">
         <v>44269</v>
       </c>
@@ -5101,7 +5101,7 @@
         <v>170836</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="61">
         <v>44270</v>
       </c>
@@ -5115,7 +5115,7 @@
         <v>247208</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="61">
         <v>44271</v>
       </c>
@@ -5129,7 +5129,7 @@
         <v>179980</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="61">
         <v>44272</v>
       </c>
@@ -5143,7 +5143,7 @@
         <v>203656</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="61">
         <v>44273</v>
       </c>
@@ -5157,7 +5157,7 @@
         <v>193822</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="61">
         <v>44274</v>
       </c>
@@ -5171,7 +5171,7 @@
         <v>240765</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="61">
         <v>44275</v>
       </c>
@@ -5185,7 +5185,7 @@
         <v>218349</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="61">
         <v>44276</v>
       </c>
@@ -5199,7 +5199,7 @@
         <v>165457</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="61">
         <v>44277</v>
       </c>
@@ -5213,7 +5213,7 @@
         <v>264519</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="61">
         <v>44278</v>
       </c>
@@ -5227,7 +5227,7 @@
         <v>296265</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="61">
         <v>44279</v>
       </c>
@@ -5241,7 +5241,7 @@
         <v>328841</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="61">
         <v>44280</v>
       </c>
@@ -5255,7 +5255,7 @@
         <v>331862</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="61">
         <v>44281</v>
       </c>
@@ -5269,7 +5269,7 @@
         <v>366506</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="61">
         <v>44282</v>
       </c>
@@ -5283,7 +5283,7 @@
         <v>282920</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="61">
         <v>44283</v>
       </c>
@@ -5297,7 +5297,7 @@
         <v>194607</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="61">
         <v>44284</v>
       </c>
@@ -5311,7 +5311,7 @@
         <v>304272</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="61">
         <v>44285</v>
       </c>
@@ -5325,7 +5325,7 @@
         <v>321473</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="61">
         <v>44286</v>
       </c>
@@ -5339,7 +5339,7 @@
         <v>333467</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="61">
         <v>44287</v>
       </c>
@@ -5353,7 +5353,7 @@
         <v>316748</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" s="61">
         <v>44288</v>
       </c>
@@ -5367,7 +5367,7 @@
         <v>227557</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" s="61">
         <v>44289</v>
       </c>
@@ -5381,7 +5381,7 @@
         <v>228917</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" s="61">
         <v>44290</v>
       </c>
@@ -5395,7 +5395,7 @@
         <v>194871</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="61">
         <v>44291</v>
       </c>
@@ -5409,7 +5409,7 @@
         <v>249215</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="61">
         <v>44292</v>
       </c>
@@ -5423,7 +5423,7 @@
         <v>374517</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" s="61">
         <v>44293</v>
       </c>
@@ -5437,7 +5437,7 @@
         <v>668171</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="61">
         <v>44294</v>
       </c>
@@ -5451,7 +5451,7 @@
         <v>717884</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" s="61">
         <v>44295</v>
       </c>
@@ -5465,7 +5465,7 @@
         <v>599285</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="61">
         <v>44296</v>
       </c>
@@ -5479,7 +5479,7 @@
         <v>347150</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" s="61">
         <v>44297</v>
       </c>
@@ -5493,13 +5493,13 @@
         <v>247428</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" s="61"/>
       <c r="B108" s="65"/>
       <c r="C108" s="65"/>
       <c r="D108" s="65"/>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" s="61" t="s">
         <v>19</v>
       </c>
@@ -5513,18 +5513,18 @@
         <v>18231747</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" s="63"/>
       <c r="B110" s="64"/>
       <c r="C110" s="64"/>
       <c r="D110" s="64"/>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" s="62" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" s="62" t="s">
         <v>78</v>
       </c>
